--- a/preview/pr-21/CodeSystem-ansocq-koerperteile.xlsx
+++ b/preview/pr-21/CodeSystem-ansocq-koerperteile.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T12:55:11+00:00</t>
+    <t>2026-10-01T13:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-21/CodeSystem-ansocq-koerperteile.xlsx
+++ b/preview/pr-21/CodeSystem-ansocq-koerperteile.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:01:03+00:00</t>
+    <t>2026-10-01T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
